--- a/data/contractors/c9.xlsx
+++ b/data/contractors/c9.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R36d25f4cba464d7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" r:id="R8c6d19d6d39e49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модель" sheetId="3" r:id="R6298d1be95d54a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATA" sheetId="4" r:id="Rb09d8497609646e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Ra0cff61e0c794e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" r:id="R9362485d539741f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модель" sheetId="3" r:id="R74a5092c5d4b40bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATA" sheetId="4" r:id="R8d3bbfa68a554c12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -567,7 +567,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>{"application":"financial-economic-model","fileType":"contractor","schemaVersion":1,"savedAt":"2026-09-22T19:09:50.065Z","contractor":{"id":"c9","name":"Подрядчик 9","contracts":[]}}</x:v>
+        <x:v>{"application":"financial-economic-model","fileType":"contractor","schemaVersion":1,"savedAt":"2026-09-22T19:54:09.673Z","contractor":{"id":"c9","name":"Подрядчик 9","contracts":[],"sourceMapping":{"schemaVersion":"1.0.0","editable":true,"matching":{"normalizeHeaders":true,"ignoreCase":true,"ignoreWhitespace":true,"ignorePunctuation":true,"minimumAutomaticConfidence":0.9,"requireConfirmationBelowConfidence":0.98},"sources":{"boq":{"enabled":true,"required":true,"path":"data/sources/boq.xlsx","sheetAliases":["BOQ","Ведомость объемов","Ведомость объёмов"],"headerRow":{"mode":"auto","fallback":9,"searchRows":30},"requiredFields":["item_code","item_name","unit","contract_quantity"],"fields":{"item_code":["Шифр ЕР","Код ЕР","Код расценки"],"item_name":["Наименование ЕР","Наименование работ"],"unit":["Ед. изм.","Единица измерения"],"contract_quantity":["Кол-во по BoQ","Количество по BOQ","Объем по BOQ","Объём по BOQ"],"labor_hours_unit":["Трудозатраты за ед., чел.-час."],"labor_hours_total":["Трудозатраты всего, чел.-час"],"machine_hours_unit":["Машины и механизмы за ед., маш.-час."],"machine_hours_total":["Машины и механизмы всего, маш.-час"],"smr_unit_rate":["Един. расценка на СМР прямые затраты, USD"],"materials_unit_rate":["Един. расценка стоимости материалов и оборудования, USD"],"kq_code":["Код KQ-1","Код KQ-2","KQ"],"kq_name":["Наименование KQ-1","Наименование KQ-2"]}},"ksg":{"enabled":true,"required":true,"path":"data/sources/ksg.xlsx","sheetAliases":["КСГ","Календарный график","График производства"],"headerRow":{"mode":"auto","fallback":2,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"month"},"requiredFields":["kq_code","work_name","planned_quantity"],"fields":{"kq_code":["Ключевые работы","Код KQ","KQ"],"work_name":["Название работы","Наименование работы"],"work_id":["Идентификатор работы","Код работы"],"smr_rate":["Расценка СМР"],"materials_rate":["Расценка МТР"],"contract_quantity":["Контрактные объемы","Контрактные объёмы"],"planned_quantity":["Кол-во по завершении","Количество по завершении"],"actual_quantity":["Фактическое количество"],"remaining_quantity":["Оставшееся количество"],"start_date":["Начало","Дата начала"],"finish_date":["Окончание","Дата окончания"]}},"personnel":{"enabled":true,"required":true,"path":"data/sources/personnel.xlsx","sheetAliases":["Персонал","График персонала","Ресурсный график персонала"],"headerRow":{"mode":"auto","fallback":4,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"day"},"requiredFields":["contractor","category","work_name","personnel_type"],"fields":{"source_key":["Ключ"],"contractor":["Подрядчик","Контрагент"],"facility":["Установка","Объект"],"title":["Титул"],"category":["Категория"],"kq_code":["KQ","Код KQ"],"discipline":["Дисциплина"],"work_name":["Наименование работ","Работа"],"personnel_type":["Персонал","Профессия","Категория персонала"]}},"equipment":{"enabled":true,"required":true,"path":"data/sources/equipment.xlsx","sheetAliases":["Техника","График техники","Ресурсный график техники"],"headerRow":{"mode":"auto","fallback":4,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"day"},"requiredFields":["contractor","equipment_type","equipment_name","work_name"],"fields":{"source_key":["Ключ"],"contractor":["Подрядчик","Контрагент"],"facility":["Установка","Объект"],"title":["Титул"],"category":["Категория"],"equipment_type":["Тип техники","Группа техники"],"equipment_name":["Техника","Наименование техники"],"work_name":["Наименование работ","Работа"],"kq_code":["KQ","Код KQ"],"discipline":["Дисциплина"]}},"primary_documents":{"enabled":true,"required":true,"path":"data/sources/primary_documents.xlsx","sheetAliases":["Первичка в вал.контракта","Первичка","КС и первичные документы"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["contractor","contract_number","currency","document_number","document_date","amount_without_vat"],"fields":{"contractor":["Контрагент","Подрядчик"],"contractor_code":["Код КА"],"legal_entity":["ЮЛ","Юридическое лицо"],"expense_type":["Вид расхода"],"contract_number":["Договор с КА","Договор","Номер договора"],"project":["Проект"],"currency":["Валюта"],"vat_rate":["Ставка НДС","НДС"],"document_number":["№ КС-3, ПУД, ТОРГ-12","Номер КС-3","Номер документа"],"document_date":["Дата КС-3","Дата подписания КС"],"amount_without_vat":["Сумма без НДС"],"services_without_vat":["Услуги без НДС"],"materials_without_vat":["МТР П без НДС"],"amount_with_vat":["Сумма с НДС"],"guarantee_rate":["% ГУ"],"guarantee_without_vat":["сумма ГУ без НДС"],"advance_offset_without_vat":["Аванс зачет без НДС","Аванс зачёт без НДС"],"planned_payment_date":["ПЛАН ОПЛАТЫ ДАТА","Плановая дата оплаты"],"actual_payment_without_vat":["Факт оплаты по КС без НДС"],"actual_payment_date":["Дата оплаты факт"]}},"payments":{"enabled":true,"required":true,"path":"data/sources/payments.xlsx","sheetAliases":["Платежи","Реестр платежей","Фактические платежи"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["payment_date","contractor","contract_number","amount_without_vat"],"fields":{"payment_date":["Дата платежа"],"contractor":["Контрагент","Имя 1","КА"],"contract_number":["Номер договора","Договор"],"currency":["Валюта транзакции"],"amount_with_vat":["Финансирование, с НДС, Влт","Финансирование, руб. экв, с НДС"],"amount_without_vat":["Финансирование, без НДС, Влт","Финансирование, руб. экв, без НДС"],"payment_purpose":["Назначение платежа"],"payment_type":["Вид оплаты (аванс, оплата по факту)"],"expense_type":["Вид расхода-формулу снизу протянуть","Вид расхода"]}},"factoring":{"enabled":true,"required":false,"path":"data/sources/factoring.xlsx","sheetAliases":["Факторинг","Реестр факторинга"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["contractor","contract_number","document_number","financed_amount"],"fields":{"contractor":["Контрагент","Подрядчик"],"project":["Проект"],"factoring_contract":["Договор на факторинге"],"contract_number":["Договор","Номер договора"],"bank":["Банк"],"financed_amount":["Оплаченная сумма банком"],"document_number":["Номер КС-3"],"document_date":["Дата КС-3"],"financing_start_date":["Дата начала начисления Процентов за пользование коммерческим кредитом3"],"financing_end_date":["Дата окончания периода коммерческого кредита6"],"amount_with_vat_currency":["Сумма в евро / Доллар с НДС"],"exchange_rate":["курс евро / доллар","Курс"],"amount_without_vat_currency":["Сумма в евро / Доллар без НДС"],"payment_date":["Дата платежа"],"amount_without_vat_rub":["Оплачено без НДС в руб."]}}}}}}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
